--- a/results/demand/P3_isru_zbo_replanned_TEAM_LOW_DEMAND/results.xlsx
+++ b/results/demand/P3_isru_zbo_replanned_TEAM_LOW_DEMAND/results.xlsx
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,6 +1543,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -11557,18 +11590,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11581,7 +11614,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11606,18 +11639,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11630,7 +11663,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11655,18 +11688,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11679,7 +11712,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11704,18 +11737,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11728,7 +11761,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11753,18 +11786,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11777,7 +11810,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11802,18 +11835,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -11826,7 +11859,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11851,7 +11884,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -11875,7 +11908,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12086,7 +12119,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -12110,7 +12143,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12321,11 +12354,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>24.65766075000005</v>
+        <v>20.35771375000003</v>
       </c>
       <c r="G45" t="n">
         <v>70</v>
@@ -12345,7 +12378,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12589,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -12580,7 +12613,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12889,7 +12922,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -12913,7 +12946,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13222,7 +13255,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -13246,7 +13279,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/demand/P3_isru_zbo_replanned_TEAM_LOW_DEMAND/results.xlsx
+++ b/results/demand/P3_isru_zbo_replanned_TEAM_LOW_DEMAND/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,6 +1575,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/demand/P3_isru_zbo_replanned_TEAM_LOW_DEMAND/results.xlsx
+++ b/results/demand/P3_isru_zbo_replanned_TEAM_LOW_DEMAND/results.xlsx
@@ -7538,7 +7538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7647,6 +7647,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7722,6 +7727,9 @@
       <c r="U2" t="n">
         <v>1.54917</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7797,6 +7805,9 @@
       <c r="U3" t="n">
         <v>39.55545</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7872,6 +7883,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7947,6 +7961,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8022,6 +8039,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8097,6 +8117,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8172,6 +8195,9 @@
       <c r="U8" t="n">
         <v>55.0989</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8247,6 +8273,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8322,6 +8351,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8397,6 +8429,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8472,6 +8507,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8547,6 +8585,9 @@
       <c r="U13" t="n">
         <v>73.14794999999999</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8622,6 +8663,9 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8697,6 +8741,9 @@
       <c r="U15" t="n">
         <v>0</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8772,6 +8819,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8847,6 +8897,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8922,6 +8975,9 @@
       <c r="U18" t="n">
         <v>49.2381</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8997,6 +9053,9 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9072,6 +9131,9 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9147,6 +9209,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9222,6 +9287,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9297,6 +9365,9 @@
       <c r="U23" t="n">
         <v>65.7441</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9372,6 +9443,9 @@
       <c r="U24" t="n">
         <v>0</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9447,6 +9521,9 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9522,6 +9599,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9597,6 +9677,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9672,6 +9755,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9747,6 +9833,9 @@
       <c r="U29" t="n">
         <v>0.8684999999999999</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9822,6 +9911,9 @@
       <c r="U30" t="n">
         <v>0</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9897,6 +9989,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9970,6 +10065,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9984,7 +10082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10048,6 +10146,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10090,6 +10193,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10132,6 +10238,9 @@
       <c r="L3" t="n">
         <v>1250</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10174,6 +10283,9 @@
       <c r="L4" t="n">
         <v>1430</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10216,6 +10328,9 @@
       <c r="L5" t="n">
         <v>1430</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10258,6 +10373,9 @@
       <c r="L6" t="n">
         <v>1430</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10299,6 +10417,9 @@
       </c>
       <c r="L7" t="n">
         <v>1430</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -20941,7 +21062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21379,11 +21500,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9.863049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -21399,11 +21520,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>38.46601275000013</v>
+        <v>9.863049</v>
       </c>
     </row>
     <row r="24">
@@ -21419,11 +21540,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>38.46601275000013</v>
       </c>
     </row>
     <row r="25">
@@ -21439,7 +21560,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -21459,7 +21580,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -21479,11 +21600,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -21499,11 +21620,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>71</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -21519,10 +21640,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>71</v>
       </c>
     </row>

--- a/results/demand/P3_isru_zbo_replanned_TEAM_LOW_DEMAND/results.xlsx
+++ b/results/demand/P3_isru_zbo_replanned_TEAM_LOW_DEMAND/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -870,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,7 +1396,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1414,24 +1416,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1441,29 +1443,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1473,29 +1475,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1505,176 +1507,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9.863049</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9.863049</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.29589147</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2411,6 +2556,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2483,6 +2638,12 @@
         <v>0.6016461000000001</v>
       </c>
       <c r="U2" t="n">
+        <v>16.85848766666667</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>7.325066666666667</v>
       </c>
     </row>
@@ -2554,6 +2715,12 @@
         <v>0.62137242</v>
       </c>
       <c r="U3" t="n">
+        <v>17.18725966666667</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>7.325066666666667</v>
       </c>
     </row>
@@ -2625,6 +2792,12 @@
         <v>0.6410987400000001</v>
       </c>
       <c r="U4" t="n">
+        <v>17.51603166666667</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>7.325066666666667</v>
       </c>
     </row>
@@ -2696,6 +2869,12 @@
         <v>0.6608250600000002</v>
       </c>
       <c r="U5" t="n">
+        <v>17.84480366666667</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>7.325066666666667</v>
       </c>
     </row>
@@ -2767,6 +2946,12 @@
         <v>0.6805513800000002</v>
       </c>
       <c r="U6" t="n">
+        <v>18.17357566666667</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>7.325066666666667</v>
       </c>
     </row>
@@ -2838,6 +3023,12 @@
         <v>0.7002777000000003</v>
       </c>
       <c r="U7" t="n">
+        <v>18.50234766666667</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>7.325066666666667</v>
       </c>
     </row>
@@ -2909,6 +3100,12 @@
         <v>0.7200040200000003</v>
       </c>
       <c r="U8" t="n">
+        <v>18.83111966666667</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>7.325066666666667</v>
       </c>
     </row>
@@ -2980,6 +3177,12 @@
         <v>0.7397303400000004</v>
       </c>
       <c r="U9" t="n">
+        <v>19.15989166666667</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>7.325066666666667</v>
       </c>
     </row>
@@ -3051,6 +3254,12 @@
         <v>0.7594566600000004</v>
       </c>
       <c r="U10" t="n">
+        <v>19.48866366666667</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>7.325066666666667</v>
       </c>
     </row>
@@ -3122,6 +3331,12 @@
         <v>0.7791829800000004</v>
       </c>
       <c r="U11" t="n">
+        <v>19.81743566666668</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>7.325066666666667</v>
       </c>
     </row>
@@ -3193,6 +3408,12 @@
         <v>0.7989093000000005</v>
       </c>
       <c r="U12" t="n">
+        <v>20.14620766666668</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>7.325066666666667</v>
       </c>
     </row>
@@ -3264,6 +3485,12 @@
         <v>0.8186356200000006</v>
       </c>
       <c r="U13" t="n">
+        <v>20.47497966666668</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>7.325066666666667</v>
       </c>
     </row>
@@ -3335,6 +3562,12 @@
         <v>0.8408276225000004</v>
       </c>
       <c r="U14" t="n">
+        <v>23.55260775000001</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>10.20345</v>
       </c>
     </row>
@@ -3406,6 +3639,12 @@
         <v>0.8654853075000005</v>
       </c>
       <c r="U15" t="n">
+        <v>23.96356916666668</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>10.20345</v>
       </c>
     </row>
@@ -3477,6 +3716,12 @@
         <v>0.8901429925000005</v>
       </c>
       <c r="U16" t="n">
+        <v>24.37453058333334</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>10.20345</v>
       </c>
     </row>
@@ -3548,6 +3793,12 @@
         <v>0.9148006775000005</v>
       </c>
       <c r="U17" t="n">
+        <v>24.78549200000001</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>10.20345</v>
       </c>
     </row>
@@ -3619,6 +3870,12 @@
         <v>0.9394583625000004</v>
       </c>
       <c r="U18" t="n">
+        <v>25.19645341666667</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>10.20345</v>
       </c>
     </row>
@@ -3690,6 +3947,12 @@
         <v>0.9641160475000005</v>
       </c>
       <c r="U19" t="n">
+        <v>25.60741483333334</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>10.20345</v>
       </c>
     </row>
@@ -3761,6 +4024,12 @@
         <v>0.9887737325000004</v>
       </c>
       <c r="U20" t="n">
+        <v>26.01837625000001</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>10.20345</v>
       </c>
     </row>
@@ -3832,6 +4101,12 @@
         <v>1.0134314175</v>
       </c>
       <c r="U21" t="n">
+        <v>26.42933766666668</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>10.20345</v>
       </c>
     </row>
@@ -3903,6 +4178,12 @@
         <v>1.0380891025</v>
       </c>
       <c r="U22" t="n">
+        <v>26.84029908333334</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>10.20345</v>
       </c>
     </row>
@@ -3974,6 +4255,12 @@
         <v>1.0627467875</v>
       </c>
       <c r="U23" t="n">
+        <v>27.25126050000001</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>10.20345</v>
       </c>
     </row>
@@ -4045,6 +4332,12 @@
         <v>1.0874044725</v>
       </c>
       <c r="U24" t="n">
+        <v>27.66222191666667</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>10.20345</v>
       </c>
     </row>
@@ -4116,6 +4409,12 @@
         <v>1.1120621575</v>
       </c>
       <c r="U25" t="n">
+        <v>28.07318333333334</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>10.20345</v>
       </c>
     </row>
@@ -4187,6 +4486,12 @@
         <v>1.13248031875</v>
       </c>
       <c r="U26" t="n">
+        <v>31.676160625</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>13.545875</v>
       </c>
     </row>
@@ -4258,6 +4563,12 @@
         <v>1.14865895625</v>
       </c>
       <c r="U27" t="n">
+        <v>31.94580458333334</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>13.545875</v>
       </c>
     </row>
@@ -4329,6 +4640,12 @@
         <v>1.16483759375</v>
       </c>
       <c r="U28" t="n">
+        <v>32.21544854166667</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>13.545875</v>
       </c>
     </row>
@@ -4400,6 +4717,12 @@
         <v>1.181016231250001</v>
       </c>
       <c r="U29" t="n">
+        <v>32.48509250000001</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>13.545875</v>
       </c>
     </row>
@@ -4471,6 +4794,12 @@
         <v>1.197194868750001</v>
       </c>
       <c r="U30" t="n">
+        <v>32.75473645833335</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>13.545875</v>
       </c>
     </row>
@@ -4542,6 +4871,12 @@
         <v>1.213373506250002</v>
       </c>
       <c r="U31" t="n">
+        <v>33.02438041666669</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>13.545875</v>
       </c>
     </row>
@@ -4613,6 +4948,12 @@
         <v>1.242962560000002</v>
       </c>
       <c r="U32" t="n">
+        <v>33.74103825000003</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>13.545875</v>
       </c>
     </row>
@@ -4684,6 +5025,12 @@
         <v>1.285962030000002</v>
       </c>
       <c r="U33" t="n">
+        <v>34.45769608333337</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>13.545875</v>
       </c>
     </row>
@@ -4755,6 +5102,12 @@
         <v>1.328961500000002</v>
       </c>
       <c r="U34" t="n">
+        <v>35.1743539166667</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>13.545875</v>
       </c>
     </row>
@@ -4826,6 +5179,12 @@
         <v>1.371960970000002</v>
       </c>
       <c r="U35" t="n">
+        <v>35.89101175000004</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>13.545875</v>
       </c>
     </row>
@@ -4897,6 +5256,12 @@
         <v>1.414960440000002</v>
       </c>
       <c r="U36" t="n">
+        <v>36.60766958333338</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>13.545875</v>
       </c>
     </row>
@@ -4968,6 +5333,12 @@
         <v>1.457959910000003</v>
       </c>
       <c r="U37" t="n">
+        <v>37.32432741666671</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>13.545875</v>
       </c>
     </row>
@@ -5039,6 +5410,12 @@
         <v>1.249720129000003</v>
       </c>
       <c r="U38" t="n">
+        <v>33.66634355000005</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>9.1181</v>
       </c>
     </row>
@@ -5110,6 +5487,12 @@
         <v>0.7902410970000026</v>
       </c>
       <c r="U39" t="n">
+        <v>26.00835968333337</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>9.1181</v>
       </c>
     </row>
@@ -5181,6 +5564,12 @@
         <v>0.6271620650000025</v>
       </c>
       <c r="U40" t="n">
+        <v>28.23037581666671</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>9.1181</v>
       </c>
     </row>
@@ -5252,6 +5641,12 @@
         <v>0.7604830330000022</v>
       </c>
       <c r="U41" t="n">
+        <v>30.45239195000004</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>9.1181</v>
       </c>
     </row>
@@ -5323,6 +5718,12 @@
         <v>0.8938040010000021</v>
       </c>
       <c r="U42" t="n">
+        <v>32.67440808333337</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>9.1181</v>
       </c>
     </row>
@@ -5394,6 +5795,12 @@
         <v>1.027124969000002</v>
       </c>
       <c r="U43" t="n">
+        <v>34.8964242166667</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>9.1181</v>
       </c>
     </row>
@@ -5465,6 +5872,12 @@
         <v>1.160445937000002</v>
       </c>
       <c r="U44" t="n">
+        <v>37.11844035000003</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>9.1181</v>
       </c>
     </row>
@@ -5536,6 +5949,12 @@
         <v>1.293766905000001</v>
       </c>
       <c r="U45" t="n">
+        <v>39.34045648333336</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>9.1181</v>
       </c>
     </row>
@@ -5607,6 +6026,12 @@
         <v>1.427087873000001</v>
       </c>
       <c r="U46" t="n">
+        <v>41.56247261666668</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>9.1181</v>
       </c>
     </row>
@@ -5678,6 +6103,12 @@
         <v>1.560408841000001</v>
       </c>
       <c r="U47" t="n">
+        <v>43.78448875000001</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>9.1181</v>
       </c>
     </row>
@@ -5749,6 +6180,12 @@
         <v>1.693729809</v>
       </c>
       <c r="U48" t="n">
+        <v>46.00650488333333</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>9.1181</v>
       </c>
     </row>
@@ -5820,6 +6257,12 @@
         <v>1.827050777</v>
       </c>
       <c r="U49" t="n">
+        <v>48.22852101666666</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>9.1181</v>
       </c>
     </row>
@@ -5891,6 +6334,12 @@
         <v>1.910971591999999</v>
       </c>
       <c r="U50" t="n">
+        <v>53.47053204999999</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>12.174775</v>
       </c>
     </row>
@@ -5962,6 +6411,12 @@
         <v>1.945492253999999</v>
       </c>
       <c r="U51" t="n">
+        <v>54.04587641666666</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>12.174775</v>
       </c>
     </row>
@@ -6033,6 +6488,12 @@
         <v>1.980012916</v>
       </c>
       <c r="U52" t="n">
+        <v>54.62122078333333</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>12.174775</v>
       </c>
     </row>
@@ -6104,6 +6565,12 @@
         <v>2.014533578</v>
       </c>
       <c r="U53" t="n">
+        <v>55.19656515</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>12.174775</v>
       </c>
     </row>
@@ -6175,6 +6642,12 @@
         <v>2.04905424</v>
       </c>
       <c r="U54" t="n">
+        <v>55.77190951666667</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>12.174775</v>
       </c>
     </row>
@@ -6246,6 +6719,12 @@
         <v>2.083574902</v>
       </c>
       <c r="U55" t="n">
+        <v>56.34725388333334</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>12.174775</v>
       </c>
     </row>
@@ -6317,6 +6796,12 @@
         <v>2.118095564</v>
       </c>
       <c r="U56" t="n">
+        <v>56.92259825000001</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>12.174775</v>
       </c>
     </row>
@@ -6388,6 +6873,12 @@
         <v>2.152616226000001</v>
       </c>
       <c r="U57" t="n">
+        <v>57.49794261666668</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>12.174775</v>
       </c>
     </row>
@@ -6459,6 +6950,12 @@
         <v>2.187136888000001</v>
       </c>
       <c r="U58" t="n">
+        <v>58.07328698333335</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>12.174775</v>
       </c>
     </row>
@@ -6530,6 +7027,12 @@
         <v>2.221657550000001</v>
       </c>
       <c r="U59" t="n">
+        <v>58.64863135000002</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>12.174775</v>
       </c>
     </row>
@@ -6601,6 +7104,12 @@
         <v>2.256178212000001</v>
       </c>
       <c r="U60" t="n">
+        <v>59.22397571666669</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>12.174775</v>
       </c>
     </row>
@@ -6672,6 +7181,12 @@
         <v>2.290698874000002</v>
       </c>
       <c r="U61" t="n">
+        <v>59.79932008333336</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>12.174775</v>
       </c>
     </row>
@@ -6743,6 +7258,12 @@
         <v>2.307959270000002</v>
       </c>
       <c r="U62" t="n">
+        <v>64.46598891666669</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6814,6 +7335,12 @@
         <v>2.307959400000002</v>
       </c>
       <c r="U63" t="n">
+        <v>64.46599108333336</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6885,6 +7412,12 @@
         <v>2.307959530000003</v>
       </c>
       <c r="U64" t="n">
+        <v>64.46599325000004</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6956,6 +7489,12 @@
         <v>2.307959660000003</v>
       </c>
       <c r="U65" t="n">
+        <v>64.46599541666671</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7027,6 +7566,12 @@
         <v>2.307959790000004</v>
       </c>
       <c r="U66" t="n">
+        <v>64.46599758333339</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7098,6 +7643,12 @@
         <v>2.307959920000004</v>
       </c>
       <c r="U67" t="n">
+        <v>64.46599975000007</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7169,6 +7720,12 @@
         <v>2.307960050000005</v>
       </c>
       <c r="U68" t="n">
+        <v>64.46600191666674</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7240,6 +7797,12 @@
         <v>2.307960180000006</v>
       </c>
       <c r="U69" t="n">
+        <v>64.46600408333342</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7311,6 +7874,12 @@
         <v>2.307960310000006</v>
       </c>
       <c r="U70" t="n">
+        <v>64.46600625000009</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7382,6 +7951,12 @@
         <v>2.307960440000007</v>
       </c>
       <c r="U71" t="n">
+        <v>64.46600841666677</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7453,6 +8028,12 @@
         <v>2.307960570000007</v>
       </c>
       <c r="U72" t="n">
+        <v>64.46601058333344</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7524,6 +8105,12 @@
         <v>2.307960700000007</v>
       </c>
       <c r="U73" t="n">
+        <v>64.46601275000012</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10173,7 +10760,7 @@
         <v>41.10462</v>
       </c>
       <c r="F2" t="n">
-        <v>8.521690320000003</v>
+        <v>8.817581790000004</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10182,13 +10769,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>686.5286903199999</v>
+        <v>686.8245817899999</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>686.5286903199999</v>
+        <v>686.8245817899999</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -10454,7 +11041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12145,7 +12732,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -12153,14 +12740,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>87.901</v>
+        <v>20.47497966666668</v>
       </c>
       <c r="G36" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -12177,7 +12764,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12194,7 +12781,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -12202,14 +12789,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>87.9008</v>
+        <v>87.901</v>
       </c>
       <c r="G37" t="n">
-        <v>87.901</v>
+        <v>190</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -12243,7 +12830,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -12251,18 +12838,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>87.9008</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <f>=</f>
-        <v/>
+        <v>87.901</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -12272,7 +12860,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12287,7 +12879,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -12295,7 +12887,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -12331,27 +12923,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>18.73985</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -12361,11 +12952,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12380,7 +12967,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -12388,14 +12975,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>122.442</v>
+        <v>18.73985</v>
       </c>
       <c r="G41" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -12412,7 +12999,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12429,7 +13016,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -12437,14 +13024,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>122.4414</v>
+        <v>28.07318333333334</v>
       </c>
       <c r="G42" t="n">
-        <v>122.442</v>
+        <v>70</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -12461,7 +13048,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12478,7 +13065,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -12486,170 +13073,170 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>122.442</v>
+      </c>
+      <c r="G43" t="n">
+        <v>190</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>122.4414</v>
+      </c>
+      <c r="G44" t="n">
+        <v>122.442</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45">
         <f>=</f>
         <v/>
       </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D46" t="n">
         <v>2036</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44">
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46">
         <f>=</f>
         <v/>
       </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>20.35771375000003</v>
-      </c>
-      <c r="G45" t="n">
-        <v>70</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2037-06, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>162.551</v>
-      </c>
-      <c r="G46" t="n">
-        <v>190</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12664,7 +13251,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -12672,14 +13259,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>162.5505</v>
+        <v>20.35771375000003</v>
       </c>
       <c r="G47" t="n">
-        <v>162.551</v>
+        <v>70</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -12696,7 +13283,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12713,7 +13300,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -12721,219 +13308,219 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>33.02438041666669</v>
+      </c>
+      <c r="G48" t="n">
+        <v>70</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2037-06, хранилище BASE; поставка одной партией в начале месяца</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>162.551</v>
+      </c>
+      <c r="G49" t="n">
+        <v>190</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>162.5505</v>
+      </c>
+      <c r="G50" t="n">
+        <v>162.551</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48">
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51">
         <f>=</f>
         <v/>
       </c>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D52" t="n">
         <v>2037</v>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49">
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52">
         <f>=</f>
         <v/>
       </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>31.56185434999999</v>
-      </c>
-      <c r="G50" t="n">
-        <v>120</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>2038-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>109.418</v>
-      </c>
-      <c r="G51" t="n">
-        <v>190</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>109.4172</v>
-      </c>
-      <c r="G52" t="n">
-        <v>109.418</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12948,7 +13535,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -12956,11 +13543,11 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>120</v>
+        <v>31.56185434999999</v>
       </c>
       <c r="G53" t="n">
         <v>120</v>
@@ -12980,7 +13567,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12997,7 +13584,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -13005,14 +13592,14 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>48.22852101666666</v>
       </c>
       <c r="G54" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -13029,7 +13616,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13046,7 +13633,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -13054,268 +13641,268 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>109.418</v>
+      </c>
+      <c r="G55" t="n">
+        <v>190</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>109.4172</v>
+      </c>
+      <c r="G56" t="n">
+        <v>109.418</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>120</v>
+      </c>
+      <c r="G57" t="n">
+        <v>120</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>100</v>
+      </c>
+      <c r="G58" t="n">
+        <v>100</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55">
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59">
         <f>=</f>
         <v/>
       </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D60" t="n">
         <v>2038</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56">
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60">
         <f>=</f>
         <v/>
       </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>38.46598675000003</v>
-      </c>
-      <c r="G57" t="n">
-        <v>120</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>2039-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>146.098</v>
-      </c>
-      <c r="G58" t="n">
-        <v>190</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>146.0973</v>
-      </c>
-      <c r="G59" t="n">
-        <v>146.098</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>reserved_D_t_per_year</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>120</v>
-      </c>
-      <c r="G60" t="n">
-        <v>120</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Lunar-ISRU</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -13330,7 +13917,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -13338,11 +13925,11 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>120</v>
+        <v>38.46598675000003</v>
       </c>
       <c r="G61" t="n">
         <v>120</v>
@@ -13362,7 +13949,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13966,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -13387,317 +13974,317 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>59.79932008333336</v>
+      </c>
+      <c r="G62" t="n">
+        <v>120</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2039-12, хранилище ZBO; поставка одной партией в начале месяца</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>146.098</v>
+      </c>
+      <c r="G63" t="n">
+        <v>190</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>146.0973</v>
+      </c>
+      <c r="G64" t="n">
+        <v>146.098</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>120</v>
+      </c>
+      <c r="G65" t="n">
+        <v>120</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>120</v>
+      </c>
+      <c r="G66" t="n">
+        <v>120</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62">
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67">
         <f>=</f>
         <v/>
       </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D68" t="n">
         <v>2039</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63">
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68">
         <f>=</f>
         <v/>
       </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>38.46601275000013</v>
-      </c>
-      <c r="G64" t="n">
-        <v>120</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>2040-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>190</v>
-      </c>
-      <c r="G65" t="n">
-        <v>190</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>190</v>
-      </c>
-      <c r="G66" t="n">
-        <v>190</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="G67" t="n">
-        <v>110</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>5.7895</v>
-      </c>
-      <c r="G68" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -13712,7 +14299,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -13720,11 +14307,11 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>120</v>
+        <v>38.46601275000013</v>
       </c>
       <c r="G69" t="n">
         <v>120</v>
@@ -13744,7 +14331,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13761,7 +14348,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -13769,11 +14356,11 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>120</v>
+        <v>64.46601275000012</v>
       </c>
       <c r="G70" t="n">
         <v>120</v>
@@ -13793,7 +14380,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13810,7 +14397,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -13818,72 +14405,366 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>190</v>
+      </c>
+      <c r="G71" t="n">
+        <v>190</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>190</v>
+      </c>
+      <c r="G72" t="n">
+        <v>190</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="G73" t="n">
+        <v>110</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>5.7895</v>
+      </c>
+      <c r="G74" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>120</v>
+      </c>
+      <c r="G75" t="n">
+        <v>120</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>120</v>
+      </c>
+      <c r="G76" t="n">
+        <v>120</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71">
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77">
         <f>=</f>
         <v/>
       </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>TEAM_LOW_DEMAND</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_team_low_demand</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
+      <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D78" t="n">
         <v>2040</v>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72">
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78">
         <f>=</f>
         <v/>
       </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21062,7 +21943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21104,7 +21985,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8392.866705937</v>
+        <v>8393.162597406999</v>
       </c>
     </row>
     <row r="3">
@@ -21124,7 +22005,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6872.891615734513</v>
+        <v>6873.187507204512</v>
       </c>
     </row>
     <row r="4">
@@ -21264,7 +22145,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.547542001741906</v>
+        <v>7.547808091193345</v>
       </c>
     </row>
     <row r="11">
@@ -21284,7 +22165,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.180657927818807</v>
+        <v>6.180924017270245</v>
       </c>
     </row>
     <row r="12">
@@ -21444,7 +22325,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>102.5959259370001</v>
+        <v>102.8918174070001</v>
       </c>
     </row>
     <row r="20">
@@ -21560,11 +22441,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.29589147</v>
       </c>
     </row>
     <row r="26">
@@ -21580,11 +22461,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -21600,7 +22481,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -21620,11 +22501,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -21640,11 +22521,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -21660,11 +22541,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TEAM_LOW_DEMAND</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_team_low_demand</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>71</v>
+      <c r="D32" t="n">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
